--- a/lang/et/headTags.xlsx
+++ b/lang/et/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1684">
   <si>
     <t>en</t>
   </si>
@@ -4141,6 +4141,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Inspireeritud)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (vanilje)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -4732,6 +4744,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -4955,6 +4970,12 @@
   </si>
   <si>
     <t>Talv</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Talve kollektsioon</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -5394,7 +5415,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1195"/>
+  <dimension ref="A1:B1199"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13102,52 +13123,52 @@
         <v>1374</v>
       </c>
       <c r="B963" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B964" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B965" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B967" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B968" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B969" t="s">
         <v>1383</v>
@@ -13158,132 +13179,132 @@
         <v>1384</v>
       </c>
       <c r="B970" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B971" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B972" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B973" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B974" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B975" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B976" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B977" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B978" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B979" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B980" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B981" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B982" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B983" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B984" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B985" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B986" t="s">
         <v>1405</v>
@@ -13302,228 +13323,228 @@
         <v>1408</v>
       </c>
       <c r="B988" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B989" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B990" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="B991" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B992" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B993" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B994" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="B995" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B996" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="B997" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B998" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B999" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B1000" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="B1001" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B1002" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B1003" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B1004" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B1005" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B1006" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1007" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1008" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B1009" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1010" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1011" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B1012" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B1013" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B1014" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B1015" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B1016" t="s">
         <v>1441</v>
@@ -13534,164 +13555,164 @@
         <v>1442</v>
       </c>
       <c r="B1017" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1018" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B1019" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="B1020" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B1021" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B1022" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1023" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B1024" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B1025" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B1026" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="B1027" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1028" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B1029" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="B1030" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B1031" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="B1032" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="B1033" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1034" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1035" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B1036" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1037" t="s">
         <v>1467</v>
@@ -13702,268 +13723,268 @@
         <v>1468</v>
       </c>
       <c r="B1038" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B1039" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B1040" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B1041" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B1042" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B1043" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B1044" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B1045" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B1046" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B1047" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B1048" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B1049" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B1050" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1051" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1052" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B1053" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B1054" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B1055" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B1056" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B1057" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B1058" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B1059" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B1060" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B1061" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B1062" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B1063" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B1064" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="B1065" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B1066" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B1067" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B1068" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B1069" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B1070" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B1071" t="s">
         <v>1507</v>
@@ -13990,52 +14011,52 @@
         <v>1512</v>
       </c>
       <c r="B1074" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1075" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B1076" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B1077" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B1078" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B1079" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B1080" t="s">
         <v>1520</v>
@@ -14046,196 +14067,196 @@
         <v>1521</v>
       </c>
       <c r="B1081" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B1082" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B1083" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B1084" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B1085" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1086" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B1087" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B1088" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B1089" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B1090" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1091" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1092" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B1093" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1094" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1095" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B1096" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B1097" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B1098" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B1099" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B1100" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B1101" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B1102" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B1103" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B1104" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1105" t="s">
         <v>1552</v>
@@ -14254,20 +14275,20 @@
         <v>1555</v>
       </c>
       <c r="B1107" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1108" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1109" t="s">
         <v>1559</v>
@@ -14302,156 +14323,156 @@
         <v>1566</v>
       </c>
       <c r="B1113" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1114" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B1115" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B1116" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B1117" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B1118" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1119" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1120" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1121" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B1122" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1123" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1124" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1125" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B1126" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B1127" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B1128" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1129" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1130" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1131" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1132" t="s">
         <v>1590</v>
@@ -14462,12 +14483,12 @@
         <v>1591</v>
       </c>
       <c r="B1133" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B1134" t="s">
         <v>1593</v>
@@ -14494,12 +14515,12 @@
         <v>1598</v>
       </c>
       <c r="B1137" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B1138" t="s">
         <v>1600</v>
@@ -14526,52 +14547,52 @@
         <v>1605</v>
       </c>
       <c r="B1141" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1607</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1609</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1611</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1613</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1615</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B1147" t="s">
         <v>1617</v>
@@ -14582,44 +14603,44 @@
         <v>1618</v>
       </c>
       <c r="B1148" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1149" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B1150" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B1151" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B1152" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1153" t="s">
         <v>1625</v>
@@ -14638,60 +14659,60 @@
         <v>1627</v>
       </c>
       <c r="B1155" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1156" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B1157" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B1158" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B1159" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B1160" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B1161" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1162" t="s">
         <v>1636</v>
@@ -14726,20 +14747,20 @@
         <v>1642</v>
       </c>
       <c r="B1166" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1167" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B1168" t="s">
         <v>1646</v>
@@ -14750,219 +14771,251 @@
         <v>1647</v>
       </c>
       <c r="B1169" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1170" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B1171" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="B1172" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="B1173" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B1174" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B1175" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B1176" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="B1177" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="B1178" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="B1179" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="B1180" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="B1181" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="B1182" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="B1183" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B1184" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="B1185" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="B1186" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B1187" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="B1188" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="B1189" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="B1190" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="B1191" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="B1192" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B1193" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="B1194" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1195" t="s">
-        <v>1676</v>
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>1683</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1195"/>
+  <autoFilter ref="A1:B1199"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
